--- a/artfynd/A 12261-2023 artfynd.xlsx
+++ b/artfynd/A 12261-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12261-2023 artfynd.xlsx
+++ b/artfynd/A 12261-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72105215</v>
+        <v>72105260</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556096.9079282171</v>
+        <v>557685</v>
       </c>
       <c r="R2" t="n">
-        <v>7247076.812844884</v>
+        <v>7246248</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -748,19 +743,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72105202</v>
+        <v>72105261</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bastanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556465.7978971534</v>
+        <v>557510</v>
       </c>
       <c r="R3" t="n">
-        <v>7246905.064455314</v>
+        <v>7246045</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -865,19 +840,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72105244</v>
+        <v>72105262</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557785.8714496531</v>
+        <v>556427</v>
       </c>
       <c r="R4" t="n">
-        <v>7246466.098586572</v>
+        <v>7246638</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -977,19 +937,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72105200</v>
+        <v>72105263</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,39 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bastanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557787.0109792909</v>
+        <v>556098</v>
       </c>
       <c r="R5" t="n">
-        <v>7246471.971553031</v>
+        <v>7247074</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1094,19 +1034,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72105261</v>
+        <v>72105216</v>
       </c>
       <c r="B6" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557510.0406084412</v>
+        <v>556097</v>
       </c>
       <c r="R6" t="n">
-        <v>7246044.846590578</v>
+        <v>7247077</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1206,19 +1131,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72105208</v>
+        <v>72105217</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557046.9586985785</v>
+        <v>556490</v>
       </c>
       <c r="R7" t="n">
-        <v>7245951.80160971</v>
+        <v>7246673</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1318,19 +1228,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>72105263</v>
+        <v>72105215</v>
       </c>
       <c r="B8" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556097.8000902757</v>
+        <v>556097</v>
       </c>
       <c r="R8" t="n">
-        <v>7247073.905309408</v>
+        <v>7247077</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1430,19 +1325,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>72105206</v>
+        <v>72105231</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557138.9944985231</v>
+        <v>557555</v>
       </c>
       <c r="R9" t="n">
-        <v>7246920.18417835</v>
+        <v>7246829</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,19 +1422,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72105211</v>
+        <v>72105232</v>
       </c>
       <c r="B10" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557158.8790061076</v>
+        <v>557696</v>
       </c>
       <c r="R10" t="n">
-        <v>7246930.181426917</v>
+        <v>7246633</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,19 +1519,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>72105254</v>
+        <v>72105233</v>
       </c>
       <c r="B11" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557502.8297463548</v>
+        <v>557775</v>
       </c>
       <c r="R11" t="n">
-        <v>7246007.089274487</v>
+        <v>7246450</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,19 +1616,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>72105253</v>
+        <v>72105234</v>
       </c>
       <c r="B12" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557788.9996688822</v>
+        <v>557708</v>
       </c>
       <c r="R12" t="n">
-        <v>7246540.962524579</v>
+        <v>7246260</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1878,19 +1713,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,16 +1745,11 @@
         <v>72105235</v>
       </c>
       <c r="B13" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1957,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556106.8074321345</v>
+        <v>556107</v>
       </c>
       <c r="R13" t="n">
-        <v>7247084.104679524</v>
+        <v>7247084</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1990,19 +1810,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>72105222</v>
+        <v>72105236</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556763.0397553525</v>
+        <v>556329</v>
       </c>
       <c r="R14" t="n">
-        <v>7247498.203833088</v>
+        <v>7247225</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2102,19 +1907,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,19 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>72105231</v>
+        <v>72105237</v>
       </c>
       <c r="B15" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2181,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557554.9207940932</v>
+        <v>556360</v>
       </c>
       <c r="R15" t="n">
-        <v>7246828.867327892</v>
+        <v>7247341</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2206,7 +1996,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2214,19 +2004,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>72105196</v>
+        <v>72105238</v>
       </c>
       <c r="B16" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557058.0246726904</v>
+        <v>556409</v>
       </c>
       <c r="R16" t="n">
-        <v>7247211.908543224</v>
+        <v>7247657</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2318,7 +2093,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2326,19 +2101,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>72105243</v>
+        <v>72105213</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557581.9044408021</v>
+        <v>557536</v>
       </c>
       <c r="R17" t="n">
-        <v>7246754.184010573</v>
+        <v>7246119</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2438,19 +2198,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>72105262</v>
+        <v>72105214</v>
       </c>
       <c r="B18" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556427.0065680738</v>
+        <v>556251</v>
       </c>
       <c r="R18" t="n">
-        <v>7246638.151744277</v>
+        <v>7247138</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2550,19 +2295,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>72105260</v>
+        <v>72105253</v>
       </c>
       <c r="B19" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557685.1415698701</v>
+        <v>557789</v>
       </c>
       <c r="R19" t="n">
-        <v>7246248.057438031</v>
+        <v>7246541</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,19 +2392,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>72105246</v>
+        <v>72105254</v>
       </c>
       <c r="B20" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556106.8473603077</v>
+        <v>557503</v>
       </c>
       <c r="R20" t="n">
-        <v>7247082.016454411</v>
+        <v>7246007</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2766,7 +2481,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2774,19 +2489,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>72105201</v>
+        <v>72105255</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,39 +2529,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bastanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556397.8174347207</v>
+        <v>557390</v>
       </c>
       <c r="R21" t="n">
-        <v>7247481.970085397</v>
+        <v>7245908</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2883,7 +2578,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2891,19 +2586,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>72105232</v>
+        <v>72105211</v>
       </c>
       <c r="B22" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2946,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557695.9815505972</v>
+        <v>557159</v>
       </c>
       <c r="R22" t="n">
-        <v>7246633.155055027</v>
+        <v>7246930</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3003,19 +2683,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,37 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>72105203</v>
+        <v>72105204</v>
       </c>
       <c r="B23" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3082,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556511.0887288688</v>
+        <v>556511</v>
       </c>
       <c r="R23" t="n">
-        <v>7246442.949448998</v>
+        <v>7246443</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,19 +2780,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>72105226</v>
+        <v>72105206</v>
       </c>
       <c r="B24" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556415.2011172017</v>
+        <v>557139</v>
       </c>
       <c r="R24" t="n">
-        <v>7247534.939438396</v>
+        <v>7246920</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3219,7 +2869,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3227,19 +2877,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,15 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>72105237</v>
+        <v>72105207</v>
       </c>
       <c r="B25" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3306,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556359.9591166887</v>
+        <v>557160</v>
       </c>
       <c r="R25" t="n">
-        <v>7247340.877678677</v>
+        <v>7245881</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3331,7 +2966,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3339,19 +2974,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>72105242</v>
+        <v>72105208</v>
       </c>
       <c r="B26" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3418,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557113.8466452556</v>
+        <v>557047</v>
       </c>
       <c r="R26" t="n">
-        <v>7247159.099770223</v>
+        <v>7245952</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3451,19 +3071,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>72105224</v>
+        <v>72105197</v>
       </c>
       <c r="B27" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3530,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557245.8582796701</v>
+        <v>556467</v>
       </c>
       <c r="R27" t="n">
-        <v>7245859.121941629</v>
+        <v>7247006</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3555,7 +3160,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3563,19 +3168,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,37 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>72105234</v>
+        <v>72105196</v>
       </c>
       <c r="B28" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3642,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557707.9156202851</v>
+        <v>557058</v>
       </c>
       <c r="R28" t="n">
-        <v>7246260.206977445</v>
+        <v>7247212</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3675,19 +3265,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>72105207</v>
+        <v>72105222</v>
       </c>
       <c r="B29" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3754,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557160.067465234</v>
+        <v>556763</v>
       </c>
       <c r="R29" t="n">
-        <v>7245880.857043817</v>
+        <v>7247498</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3779,7 +3354,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3787,19 +3362,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>72105245</v>
+        <v>72105223</v>
       </c>
       <c r="B30" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3866,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556989.8085153045</v>
+        <v>556892</v>
       </c>
       <c r="R30" t="n">
-        <v>7246028.84981488</v>
+        <v>7247357</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3891,7 +3451,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3899,19 +3459,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,15 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>72105238</v>
+        <v>72105224</v>
       </c>
       <c r="B31" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3954,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556409.0939766183</v>
+        <v>557246</v>
       </c>
       <c r="R31" t="n">
-        <v>7247656.798223044</v>
+        <v>7245859</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4003,7 +3548,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4011,19 +3556,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,15 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>72105223</v>
+        <v>72105225</v>
       </c>
       <c r="B32" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4090,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556892.0842258766</v>
+        <v>556389</v>
       </c>
       <c r="R32" t="n">
-        <v>7247356.996201952</v>
+        <v>7247499</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4123,19 +3653,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,37 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>72105214</v>
+        <v>72105226</v>
       </c>
       <c r="B33" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556250.9233942025</v>
+        <v>556415</v>
       </c>
       <c r="R33" t="n">
-        <v>7247137.834727272</v>
+        <v>7247535</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,19 +3750,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4274,37 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>72105225</v>
+        <v>72105203</v>
       </c>
       <c r="B34" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4314,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556389.126799955</v>
+        <v>556511</v>
       </c>
       <c r="R34" t="n">
-        <v>7247498.93044447</v>
+        <v>7246443</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4339,7 +3839,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4347,19 +3847,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4386,15 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>72105247</v>
+        <v>72105200</v>
       </c>
       <c r="B35" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4402,34 +3887,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bastanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556313.9189918695</v>
+        <v>557787</v>
       </c>
       <c r="R35" t="n">
-        <v>7247190.013102182</v>
+        <v>7246472</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4451,7 +3941,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Tärna</t>
+          <t>Stensele</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4459,19 +3949,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,15 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>72105233</v>
+        <v>72105201</v>
       </c>
       <c r="B36" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4514,34 +3989,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bastanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557774.8918665332</v>
+        <v>556398</v>
       </c>
       <c r="R36" t="n">
-        <v>7246450.002372555</v>
+        <v>7247482</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4563,7 +4043,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4571,19 +4051,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,15 +4080,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>72105255</v>
+        <v>72105202</v>
       </c>
       <c r="B37" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4626,34 +4091,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bastanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557390.113359406</v>
+        <v>556466</v>
       </c>
       <c r="R37" t="n">
-        <v>7245907.915616585</v>
+        <v>7246905</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4675,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Stensele</t>
+          <t>Tärna</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4683,19 +4153,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4719,790 +4179,6 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>72105204</v>
-      </c>
-      <c r="B38" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Bastanliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>556511.0887288688</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7246442.949448998</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>72105248</v>
-      </c>
-      <c r="B39" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Bastanliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>556424.9952024795</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7247612.825560006</v>
-      </c>
-      <c r="S39" t="n">
-        <v>5</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>72105213</v>
-      </c>
-      <c r="B40" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Bastanliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>557536.2061394812</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7246118.918229637</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>72105197</v>
-      </c>
-      <c r="B41" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Bastanliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>556467.1982294357</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7247006.203348569</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>72105236</v>
-      </c>
-      <c r="B42" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Bastanliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>556329.1421007705</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7247224.981157999</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>72105216</v>
-      </c>
-      <c r="B43" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>658</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Bastanliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>556096.9079282171</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7247076.812844884</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>72105217</v>
-      </c>
-      <c r="B44" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>658</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Bastanliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>556489.9214981627</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7246673.208742158</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
